--- a/artfynd/A 58462-2021 artfynd.xlsx
+++ b/artfynd/A 58462-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136315177</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136318545</v>
       </c>
       <c r="B3" t="n">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58462-2021 artfynd.xlsx
+++ b/artfynd/A 58462-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136315177</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136318545</v>
       </c>
       <c r="B3" t="n">
-        <v>58830</v>
+        <v>58843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
